--- a/Water_18O_Report.xlsx
+++ b/Water_18O_Report.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-3.75</v>
+        <v>-3.66</v>
       </c>
       <c r="C2" t="n">
         <v>0.17</v>
@@ -462,13 +462,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29.11</v>
-      </c>
-      <c r="C3" t="n">
-        <v>31.48</v>
-      </c>
+        <v>-2.28</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -478,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-13.85</v>
+        <v>-13.94</v>
       </c>
       <c r="C4" t="n">
         <v>0.19</v>
@@ -494,7 +492,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-11.92</v>
+        <v>-12.01</v>
       </c>
       <c r="C5" t="n">
         <v>0.16</v>
@@ -510,7 +508,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-6.24</v>
+        <v>-6.31</v>
       </c>
       <c r="C6" t="n">
         <v>0.32</v>
@@ -526,7 +524,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.39</v>
+        <v>-3.46</v>
       </c>
       <c r="C7" t="n">
         <v>0.15</v>
@@ -542,7 +540,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-7.53</v>
+        <v>-7.6</v>
       </c>
       <c r="C8" t="n">
         <v>0.13</v>
@@ -558,7 +556,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-10.94</v>
+        <v>-11.01</v>
       </c>
       <c r="C9" t="n">
         <v>0.21</v>
@@ -574,7 +572,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-15.19</v>
+        <v>-15.25</v>
       </c>
       <c r="C10" t="n">
         <v>0.25</v>
@@ -590,7 +588,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-8.85</v>
+        <v>-8.91</v>
       </c>
       <c r="C11" t="n">
         <v>0.32</v>
@@ -606,10 +604,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-4.01</v>
+        <v>-4.06</v>
       </c>
       <c r="C12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -622,7 +620,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-6.25</v>
+        <v>-6.3</v>
       </c>
       <c r="C13" t="n">
         <v>0.12</v>
@@ -638,7 +636,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-3.89</v>
+        <v>-3.93</v>
       </c>
       <c r="C14" t="n">
         <v>0.25</v>
@@ -654,10 +652,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-5.73</v>
+        <v>-5.77</v>
       </c>
       <c r="C15" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -670,10 +668,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-3.79</v>
+        <v>-3.82</v>
       </c>
       <c r="C16" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -686,7 +684,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-5.76</v>
+        <v>-5.79</v>
       </c>
       <c r="C17" t="n">
         <v>0.14</v>
@@ -702,7 +700,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-4.22</v>
+        <v>-4.25</v>
       </c>
       <c r="C18" t="n">
         <v>0.23</v>
@@ -718,7 +716,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-15.39</v>
+        <v>-15.42</v>
       </c>
       <c r="C19" t="n">
         <v>0.22</v>
@@ -734,10 +732,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-3.22</v>
+        <v>-3.23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
@@ -750,10 +748,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2</v>
+        <v>-2.01</v>
       </c>
       <c r="C21" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -766,10 +764,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-3.28</v>
+        <v>-3.29</v>
       </c>
       <c r="C22" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
@@ -782,7 +780,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-4.98</v>
+        <v>-4.99</v>
       </c>
       <c r="C23" t="n">
         <v>0.17</v>
@@ -830,7 +828,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-15.29</v>
+        <v>-15.3</v>
       </c>
       <c r="C26" t="n">
         <v>0.25</v>
@@ -846,7 +844,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-13.4</v>
+        <v>-13.41</v>
       </c>
       <c r="C27" t="n">
         <v>0.18</v>
@@ -862,7 +860,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-8.81</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="C28" t="n">
         <v>0.12</v>
@@ -878,10 +876,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.35</v>
+        <v>-4.33</v>
       </c>
       <c r="C29" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
@@ -894,7 +892,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.61</v>
+        <v>-1.58</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
@@ -908,10 +906,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="C31" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
@@ -924,10 +922,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.79</v>
+        <v>-2.76</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="D32" t="n">
         <v>2</v>
@@ -940,7 +938,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-4.67</v>
+        <v>-4.64</v>
       </c>
       <c r="C33" t="n">
         <v>0.29</v>
@@ -956,10 +954,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-7.51</v>
+        <v>-7.48</v>
       </c>
       <c r="C34" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="D34" t="n">
         <v>2</v>
@@ -972,10 +970,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-5.86</v>
+        <v>-5.82</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="D35" t="n">
         <v>2</v>
@@ -988,7 +986,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-12.2</v>
+        <v>-12.16</v>
       </c>
       <c r="C36" t="n">
         <v>0.25</v>
@@ -1004,7 +1002,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-11.49</v>
+        <v>-11.45</v>
       </c>
       <c r="C37" t="n">
         <v>0.23</v>
@@ -1020,7 +1018,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-8.01</v>
+        <v>-7.96</v>
       </c>
       <c r="C38" t="n">
         <v>0.23</v>
@@ -1036,7 +1034,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-6.43</v>
+        <v>-6.38</v>
       </c>
       <c r="C39" t="n">
         <v>0.12</v>
@@ -1052,10 +1050,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.8</v>
+        <v>-5.74</v>
       </c>
       <c r="C40" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="D40" t="n">
         <v>2</v>
@@ -1068,7 +1066,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.5</v>
+        <v>-5.44</v>
       </c>
       <c r="C41" t="n">
         <v>0.19</v>
@@ -1084,7 +1082,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-4.6</v>
+        <v>-4.54</v>
       </c>
       <c r="C42" t="n">
         <v>0.14</v>
@@ -1100,10 +1098,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-3.83</v>
+        <v>-3.76</v>
       </c>
       <c r="C43" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="D43" t="n">
         <v>2</v>
@@ -1116,10 +1114,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-4.44</v>
+        <v>-4.37</v>
       </c>
       <c r="C44" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="D44" t="n">
         <v>2</v>
@@ -1167,7 +1165,7 @@
         <v>0.32</v>
       </c>
       <c r="C47" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="D47" t="n">
         <v>6</v>
@@ -1183,7 +1181,7 @@
         <v>-11.37</v>
       </c>
       <c r="C48" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="D48" t="n">
         <v>6</v>
@@ -1297,7 +1295,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.054260054573216</v>
+        <v>1.053231857877764</v>
       </c>
     </row>
     <row r="10">
@@ -1307,7 +1305,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.763636768514419</v>
+        <v>1.866694711662197</v>
       </c>
     </row>
   </sheetData>

--- a/Water_18O_Report.xlsx
+++ b/Water_18O_Report.xlsx
@@ -1198,7 +1198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,20 +1291,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Slope</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.053231857877764</v>
+          <t>Drift Correction Applied</t>
+        </is>
+      </c>
+      <c r="B9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Drift Monitor Used</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Slope</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.053231857877764</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B12" t="n">
         <v>1.866694711662196</v>
       </c>
     </row>
